--- a/testData/opencart_LoginData.xlsx
+++ b/testData/opencart_LoginData.xlsx
@@ -1488,7 +1488,8 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6562" style="1" customWidth="1"/>
+    <col min="2" max="5" width="16.3516" style="1" customWidth="1"/>
     <col min="6" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
